--- a/data/3.8.2/0. base-year_2015/extensions/dom_biogeochemical/F_x_dom.xlsx
+++ b/data/3.8.2/0. base-year_2015/extensions/dom_biogeochemical/F_x_dom.xlsx
@@ -1,19 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29819"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_16B9C12BCE74F115BE88D4AE129A5B1B46311FFF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Arnaud\Documents\PlaneFR\data\3.8.2\0. base-year_2015\extensions\dom_biogeochemical\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70F7AB63-94D1-40DD-A34B-6735CA385375}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="9017" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -797,7 +805,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1157,9 +1165,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:GS14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.23046875" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="50" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:201">
+    <row r="1" spans="1:201" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1366,7 +1377,7 @@
       <c r="GR1" s="2"/>
       <c r="GS1" s="2"/>
     </row>
-    <row r="2" spans="1:201">
+    <row r="2" spans="1:201" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -1601,7 +1612,7 @@
       <c r="GR2" s="2"/>
       <c r="GS2" s="2"/>
     </row>
-    <row r="3" spans="1:201">
+    <row r="3" spans="1:201" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -1946,7 +1957,7 @@
       <c r="GR3" s="2"/>
       <c r="GS3" s="2"/>
     </row>
-    <row r="4" spans="1:201">
+    <row r="4" spans="1:201" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
         <v>46</v>
       </c>
@@ -2551,12 +2562,12 @@
         <v>246</v>
       </c>
     </row>
-    <row r="5" spans="1:201">
+    <row r="5" spans="1:201" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="6" spans="1:201">
+    <row r="6" spans="1:201" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
         <v>248</v>
       </c>
@@ -3161,7 +3172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:201">
+    <row r="7" spans="1:201" x14ac:dyDescent="0.4">
       <c r="A7" s="1" t="s">
         <v>249</v>
       </c>
@@ -3766,7 +3777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:201">
+    <row r="8" spans="1:201" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
         <v>250</v>
       </c>
@@ -4371,7 +4382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:201">
+    <row r="9" spans="1:201" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
         <v>251</v>
       </c>
@@ -4976,7 +4987,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:201">
+    <row r="10" spans="1:201" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
         <v>252</v>
       </c>
@@ -5581,7 +5592,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:201">
+    <row r="11" spans="1:201" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
         <v>253</v>
       </c>
@@ -6186,7 +6197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:201">
+    <row r="12" spans="1:201" x14ac:dyDescent="0.4">
       <c r="A12" s="1" t="s">
         <v>254</v>
       </c>
@@ -6791,7 +6802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:201">
+    <row r="13" spans="1:201" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
         <v>255</v>
       </c>
@@ -7396,7 +7407,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:201">
+    <row r="14" spans="1:201" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
         <v>256</v>
       </c>
@@ -8003,11 +8014,30 @@
     </row>
   </sheetData>
   <mergeCells count="46">
-    <mergeCell ref="BD3:BF3"/>
-    <mergeCell ref="AO3:AQ3"/>
-    <mergeCell ref="J3:R3"/>
-    <mergeCell ref="DM3:DS3"/>
-    <mergeCell ref="CK3:CM3"/>
+    <mergeCell ref="GB3:GF3"/>
+    <mergeCell ref="EU2:EV2"/>
+    <mergeCell ref="FU3:GA3"/>
+    <mergeCell ref="EX3:EZ3"/>
+    <mergeCell ref="BV3:BW3"/>
+    <mergeCell ref="FU2:GN2"/>
+    <mergeCell ref="DY3:EJ3"/>
+    <mergeCell ref="GI3:GN3"/>
+    <mergeCell ref="EW2:FA2"/>
+    <mergeCell ref="CN2:CR2"/>
+    <mergeCell ref="CP3:CR3"/>
+    <mergeCell ref="FH3:FQ3"/>
+    <mergeCell ref="U3:AF3"/>
+    <mergeCell ref="FB3:FD3"/>
+    <mergeCell ref="FH2:FT2"/>
+    <mergeCell ref="DT3:DU3"/>
+    <mergeCell ref="EK3:EL3"/>
+    <mergeCell ref="U2:AQ2"/>
+    <mergeCell ref="EU3:EV3"/>
+    <mergeCell ref="CI2:CM2"/>
+    <mergeCell ref="FB2:FG2"/>
+    <mergeCell ref="BP3:BU3"/>
+    <mergeCell ref="BY3:CG3"/>
+    <mergeCell ref="FE3:FF3"/>
     <mergeCell ref="GO3:GS3"/>
     <mergeCell ref="B1:GS1"/>
     <mergeCell ref="AR2:BL2"/>
@@ -8024,31 +8054,12 @@
     <mergeCell ref="GO2:GS2"/>
     <mergeCell ref="DV3:DX3"/>
     <mergeCell ref="B3:I3"/>
+    <mergeCell ref="BD3:BF3"/>
+    <mergeCell ref="AO3:AQ3"/>
+    <mergeCell ref="J3:R3"/>
+    <mergeCell ref="DM3:DS3"/>
+    <mergeCell ref="CK3:CM3"/>
     <mergeCell ref="CV3:CW3"/>
-    <mergeCell ref="EW2:FA2"/>
-    <mergeCell ref="CN2:CR2"/>
-    <mergeCell ref="CP3:CR3"/>
-    <mergeCell ref="FH3:FQ3"/>
-    <mergeCell ref="U3:AF3"/>
-    <mergeCell ref="FB3:FD3"/>
-    <mergeCell ref="FH2:FT2"/>
-    <mergeCell ref="DT3:DU3"/>
-    <mergeCell ref="EK3:EL3"/>
-    <mergeCell ref="U2:AQ2"/>
-    <mergeCell ref="EU3:EV3"/>
-    <mergeCell ref="CI2:CM2"/>
-    <mergeCell ref="FB2:FG2"/>
-    <mergeCell ref="BP3:BU3"/>
-    <mergeCell ref="BY3:CG3"/>
-    <mergeCell ref="FE3:FF3"/>
-    <mergeCell ref="GB3:GF3"/>
-    <mergeCell ref="EU2:EV2"/>
-    <mergeCell ref="FU3:GA3"/>
-    <mergeCell ref="EX3:EZ3"/>
-    <mergeCell ref="BV3:BW3"/>
-    <mergeCell ref="FU2:GN2"/>
-    <mergeCell ref="DY3:EJ3"/>
-    <mergeCell ref="GI3:GN3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8061,15 +8072,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100CDDBE4AC5AD34144A319C175B124CDA5" ma:contentTypeVersion="7" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="e3476bb2192acac3dedd820322df381b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="df3242dc-6eaf-41b4-ba9f-f9ed2a2fc658" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5f454edc1424e9be88661d2b6322ecfc" ns2:_="">
     <xsd:import namespace="df3242dc-6eaf-41b4-ba9f-f9ed2a2fc658"/>
@@ -8231,16 +8233,48 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{55CA7DD8-9A7B-49E1-9E82-F99ACF82124B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{55CA7DD8-9A7B-49E1-9E82-F99ACF82124B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{45516087-C306-4856-A187-43B2387EAF03}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CEF010F5-6975-4515-828B-721592D232AC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="df3242dc-6eaf-41b4-ba9f-f9ed2a2fc658"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CEF010F5-6975-4515-828B-721592D232AC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{45516087-C306-4856-A187-43B2387EAF03}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
